--- a/Trắc nghiệm ôn luyện/Tester Technical/multiple_choice_sample_template_AUTOMATION_TESTING.xlsx
+++ b/Trắc nghiệm ôn luyện/Tester Technical/multiple_choice_sample_template_AUTOMATION_TESTING.xlsx
@@ -459,10 +459,10 @@
         <v>Khả năng tự động phát hiện mọi lỗi logic nghiệp vụ mà không cần con người viết kịch bản test trước — tự phát hiện lỗi không cần kịch bản</v>
       </c>
       <c r="G2" t="str">
+        <v>Hoàn toàn loại bỏ nhu cầu tuyển dụng nhân sự QA trong suốt toàn bộ dự án phần mềm — loại bỏ nhân sự QA</v>
+      </c>
+      <c r="H2" t="str">
         <v>Khả năng tự viết lại mã nguồn code sửa lỗi cho lập trình viên khi phát hiện ra bug — tự sửa code hệ thống</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Hoàn toàn loại bỏ nhu cầu tuyển dụng nhân sự QA trong suốt toàn bộ dự án phần mềm — loại bỏ nhân sự QA</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -485,10 +485,10 @@
         <v>ID — thuộc tính định danh duy nhất của phần tử HTML trên trang — locator ID duy nhất</v>
       </c>
       <c r="F3" t="str">
+        <v>TagName — tên của thẻ HTML (như &lt;div&gt;, &lt;p&gt;) — locator tên thẻ HTML</v>
+      </c>
+      <c r="G3" t="str">
         <v>XPath — đường dẫn tuyệt đối đi từ thẻ gốc HTML xuống dưới — locator đường dẫn tuyệt đối</v>
-      </c>
-      <c r="G3" t="str">
-        <v>TagName — tên của thẻ HTML (như &lt;div&gt;, &lt;p&gt;) — locator tên thẻ HTML</v>
       </c>
       <c r="H3" t="str">
         <v>LinkText — đoạn chuỗi văn bản hiển thị của thẻ liên kết — locator văn bản liên kết</v>
@@ -511,19 +511,19 @@
         <v>POM là design pattern phổ biến nhất trong Automation. Mỗi trang web (Page) được đại diện bởi một class. Khi giao diện thay đổi (ví dụ đổi ID của nút bấm), ta chỉ cần sửa ở class tương ứng mà không phải sửa ở hàng trăm file test script.</v>
       </c>
       <c r="E4" t="str">
+        <v>Tự động gửi email thông báo kết quả chạy test cho ban giám đốc hàng giờ — gửi báo cáo hàng giờ</v>
+      </c>
+      <c r="F4" t="str">
         <v>Tách biệt locator và hành vi của từng trang web thành các class độc lập, giúp code test dễ bảo trì và tái sử dụng — thiết kế POM dễ bảo trì</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Tự động vẽ lại sơ đồ cấu trúc cơ sở dữ liệu quan hệ SQL của dự án — vẽ cấu trúc database</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Mã hóa toàn bộ các kịch bản test thành các file ảnh động GIF bảo mật — mã hóa kịch bản test</v>
       </c>
-      <c r="H4" t="str">
-        <v>Tự động gửi email thông báo kết quả chạy test cho ban giám đốc hàng giờ — gửi báo cáo hàng giờ</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Absolute XPath (như `/html/body/div[1]/div[2]/button`) sẽ bị gãy ngay khi cấu trúc trang web thay đổi nhẹ (thêm 1 thẻ div). Relative XPath (như `//button[@id="submit"]`) tìm trực tiếp phần tử có thuộc tính chỉ định, bền bỉ hơn nhiều.</v>
       </c>
       <c r="E5" t="str">
+        <v>Tuyệt đối bắt buộc phải viết bằng ngôn ngữ Java; còn Tương đối viết bằng Python — giới hạn ngôn ngữ lập trình</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Tuyệt đối chạy nhanh gấp 10 lần so với đường dẫn tương đối trong mọi trường hợp — so sánh tốc độ</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Tuyệt đối chỉ chạy được trên Google Chrome; còn Tương đối chỉ chạy được trên Safari — giới hạn trình duyệt chạy</v>
+      </c>
+      <c r="H5" t="str">
         <v>Tuyệt đối bắt đầu bằng dấu gạch chéo đơn `/` đi từ gốc html (dễ gãy); Tương đối bắt đầu bằng gạch chéo kép `//` tìm trực tiếp phần tử (ổn định hơn) — bắt đầu từ gốc html vs tìm trực tiếp</v>
       </c>
-      <c r="F5" t="str">
-        <v>Tuyệt đối chỉ chạy được trên Google Chrome; còn Tương đối chỉ chạy được trên Safari — giới hạn trình duyệt chạy</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Tuyệt đối bắt buộc phải viết bằng ngôn ngữ Java; còn Tương đối viết bằng Python — giới hạn ngôn ngữ lập trình</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Tuyệt đối chạy nhanh gấp 10 lần so với đường dẫn tương đối trong mọi trường hợp — so sánh tốc độ</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -572,10 +572,10 @@
         <v>Mở trình duyệt -&gt; Nhập username -&gt; Nhập password -&gt; Bấm nút Login -&gt; Kiểm tra xem có hiển thị trang chủ không — luồng đăng nhập tự động</v>
       </c>
       <c r="F6" t="str">
+        <v>Mở trình duyệt -&gt; Thay đổi mật khẩu của admin -&gt; Gửi mã OTP về điện thoại cá nhân — luồng đổi mật khẩu</v>
+      </c>
+      <c r="G6" t="str">
         <v>Mở trình duyệt -&gt; Xóa cơ sở dữ liệu -&gt; Đóng trình duyệt -&gt; Gửi báo cáo lỗi cho khách hàng — luồng xóa dữ liệu lỗi</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Mở trình duyệt -&gt; Thay đổi mật khẩu của admin -&gt; Gửi mã OTP về điện thoại cá nhân — luồng đổi mật khẩu</v>
       </c>
       <c r="H6" t="str">
         <v>Mở trình duyệt -&gt; Vẽ sơ đồ Use Case -&gt; Thiết kế giao diện trang chủ bằng CSS — luồng thiết kế giao diện</v>
@@ -601,13 +601,13 @@
         <v>sendKeys() — dùng để truyền chuỗi ký tự vào phần tử input — gõ text sendKeys</v>
       </c>
       <c r="F7" t="str">
+        <v>getText() — dùng để lấy chuỗi văn bản hiển thị của phần tử ra ngoài — lấy text getText</v>
+      </c>
+      <c r="G7" t="str">
         <v>click() — dùng để bấm chuột vào phần tử nút bấm hoặc liên kết — click chuột click</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>clear() — dùng để xóa sạch dữ liệu text đang có sẵn trong ô nhập — clear text clear</v>
-      </c>
-      <c r="H7" t="str">
-        <v>getText() — dùng để lấy chuỗi văn bản hiển thị của phần tử ra ngoài — lấy text getText</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -627,10 +627,10 @@
         <v>Assert (Khẳng định) là trái tim của test case. Một script test không có Assert thì chỉ là một bot click chuột tự động, không có khả năng kiểm chứng tính đúng đắn của phần mềm.</v>
       </c>
       <c r="E8" t="str">
+        <v>Tự động chụp ảnh màn hình giao diện khi chạy qua các bước của test script — chụp ảnh màn hình</v>
+      </c>
+      <c r="F8" t="str">
         <v>So sánh kết quả thực tế (Actual) với kết quả mong đợi (Expected) để quyết định test case pass hay fail — so sánh đối chiếu kết quả</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Tự động chụp ảnh màn hình giao diện khi chạy qua các bước của test script — chụp ảnh màn hình</v>
       </c>
       <c r="G8" t="str">
         <v>Mở trình duyệt web ẩn danh để chạy test mà không lưu lại lịch sử — mở trình duyệt ẩn danh</v>
@@ -639,7 +639,7 @@
         <v>Xóa bỏ toàn bộ các biến dữ liệu rác trong bộ nhớ RAM của máy tính chạy test — giải phóng bộ nhớ RAM</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -685,19 +685,19 @@
         <v>Explicit Wait (đợi tường minh) linh hoạt và thông minh hơn. Nó sử dụng `ExpectedConditions` (ví dụ: đợi cho đến khi nút bấm hiển thị và có thể click được). Tránh kết hợp cả hai loại wait vì dễ gây ra thời gian chờ không đoán trước được (timeout issues).</v>
       </c>
       <c r="E10" t="str">
+        <v>Implicit Wait bắt buộc phải chạy ban đêm; còn Explicit Wait chỉ chạy ban ngày — giới hạn thời gian chạy</v>
+      </c>
+      <c r="F10" t="str">
         <v>Implicit Wait đợi chung cho tất cả các phần tử; Explicit Wait đợi riêng cho một phần tử cụ thể với một điều kiện xác định (như phần tử có thể click, hiển thị) — đợi chung toàn cục vs đợi điều kiện cụ thể</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>Implicit Wait chạy nhanh hơn Explicit Wait gấp 10 lần trong mọi điều kiện — so sánh hiệu năng tốc độ</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Implicit Wait viết bằng mã nguồn Java; còn Explicit Wait viết bằng ngôn ngữ Python — ngôn ngữ lập trình viết</v>
       </c>
-      <c r="H10" t="str">
-        <v>Implicit Wait bắt buộc phải chạy ban đêm; còn Explicit Wait chỉ chạy ban ngày — giới hạn thời gian chạy</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Sử dụng `close()` chỉ tắt tab đang hoạt động. Sử dụng `quit()` ở cuối test suite (thường đặt trong `@AfterSuite` hoặc `@AfterTest`) giúp tắt toàn bộ trình duyệt và tắt tiến trình Webdriver chạy ngầm trên hệ điều hành, tránh rò rỉ tài nguyên (process leaks).</v>
       </c>
       <c r="E11" t="str">
-        <v>close() đóng cửa sổ trình duyệt hiện tại đang active; quit() đóng toàn bộ các cửa sổ đang mở và giải phóng driver session — đóng tab hiện tại vs đóng toàn bộ kết thúc session</v>
+        <v>close() xóa sạch dữ liệu cache; còn quit() lưu lại lịch sử duyệt web của người dùng — dọn dẹp dữ liệu duyệt</v>
       </c>
       <c r="F11" t="str">
-        <v>close() xóa sạch dữ liệu cache; còn quit() lưu lại lịch sử duyệt web của người dùng — dọn dẹp dữ liệu duyệt</v>
+        <v>close() bắt buộc sử dụng cho trình duyệt Chrome; còn quit() chỉ dùng cho Firefox — giới hạn trình duyệt</v>
       </c>
       <c r="G11" t="str">
         <v>close() do dev viết; còn quit() do QA viết tài liệu đặc tả lỗi hệ thống — phân vai trò viết lệnh</v>
       </c>
       <c r="H11" t="str">
-        <v>close() bắt buộc sử dụng cho trình duyệt Chrome; còn quit() chỉ dùng cho Firefox — giới hạn trình duyệt</v>
+        <v>close() đóng cửa sổ trình duyệt hiện tại đang active; quit() đóng toàn bộ các cửa sổ đang mở và giải phóng driver session — đóng tab hiện tại vs đóng toàn bộ kết thúc session</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Khi ID thay đổi động (ví dụ sinh ngẫu nhiên dạng `login-12345`), ta phải tìm kiếm dựa trên các thuộc tính ổn định khác. Hàm `contains(text(), "...")` hoặc `contains(@class, "...")` là giải pháp định vị phần tử bền bỉ.</v>
       </c>
       <c r="E12" t="str">
-        <v>//button[contains(text(), "Đăng nhập")] — sử dụng hàm contains để tìm kiếm chuỗi văn bản chứa bên trong — tìm kiếm chuỗi văn bản mờ</v>
+        <v>//button[@id="login_button"] — sử dụng thuộc tính ID động của nút bấm — sử dụng ID động không ổn định</v>
       </c>
       <c r="F12" t="str">
         <v>/html/body/div[1]/button[1] — sử dụng đường dẫn tuyệt đối bắt buộc — đường dẫn tuyệt đối rủi ro</v>
       </c>
       <c r="G12" t="str">
-        <v>//button[@id="login_button"] — sử dụng thuộc tính ID động của nút bấm — sử dụng ID động không ổn định</v>
+        <v>//button[contains(text(), "Đăng nhập")] — sử dụng hàm contains để tìm kiếm chuỗi văn bản chứa bên trong — tìm kiếm chuỗi văn bản mờ</v>
       </c>
       <c r="H12" t="str">
         <v>//button[@class="btn"] — sử dụng class chung của tất cả các nút trên trang web — sử dụng class chung trùng lặp</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -772,19 +772,19 @@
         <v>Flaky test là thảm họa của Automation vì nó làm giảm lòng tin vào bộ test. Nguyên nhân số 1 là việc sử dụng `Thread.sleep()` cứng nhắc thay vì sử dụng Explicit Wait để đồng bộ hóa (Synchronization) theo trạng thái render của phần tử.</v>
       </c>
       <c r="E13" t="str">
-        <v>Do bất đồng bộ thời gian tải trang (mạng chậm, phần tử chưa kịp render đã tương tác) hoặc do dữ liệu test không nhất quán giữa các lần chạy — bất đồng bộ thời gian và dữ liệu test</v>
+        <v>Do vi xử lý CPU của máy chủ CI/CD bị quá nóng trong quá trình chạy test — nhiệt độ vi xử lý máy chủ</v>
       </c>
       <c r="F13" t="str">
         <v>Do lập trình viên sửa đổi cấu trúc thuật toán của database liên tục trong ngày — thay đổi cơ sở dữ liệu</v>
       </c>
       <c r="G13" t="str">
-        <v>Do vi xử lý CPU của máy chủ CI/CD bị quá nóng trong quá trình chạy test — nhiệt độ vi xử lý máy chủ</v>
+        <v>Do bất đồng bộ thời gian tải trang (mạng chậm, phần tử chưa kịp render đã tương tác) hoặc do dữ liệu test không nhất quán giữa các lần chạy — bất đồng bộ thời gian và dữ liệu test</v>
       </c>
       <c r="H13" t="str">
         <v>Do kiểm thử viên viết code test bằng tiếng Việt có dấu khiến trình duyệt không đọc hiểu được — tiếng Việt có dấu</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>Thiết lập `@BeforeMethod` (chạy trước mỗi test case) giúp đảm bảo môi trường test của mỗi test case hoàn toàn sạch sẽ, độc lập, không bị ảnh hưởng bởi dữ liệu của test case chạy trước đó.</v>
       </c>
       <c r="E14" t="str">
+        <v>Gửi báo cáo lỗi trực tiếp lên văn phòng của khách hàng thông qua đường bưu điện — gửi báo cáo bưu điện</v>
+      </c>
+      <c r="F14" t="str">
         <v>Chạy các bước chuẩn bị (như khởi tạo trình duyệt, xóa cookie, chuẩn bị dữ liệu) trước khi thực thi từng test case cụ thể — chuẩn bị môi trường test</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
+        <v>Xóa bỏ toàn bộ các file ảnh chụp lỗi màn hình cũ đã lưu trong thư mục dự án — dọn dẹp ảnh lỗi</v>
+      </c>
+      <c r="H14" t="str">
         <v>Tự động dịch mã nguồn code test sang ngôn ngữ HTML để hiển thị ra trang web — dịch mã nguồn test</v>
       </c>
-      <c r="G14" t="str">
-        <v>Gửi báo cáo lỗi trực tiếp lên văn phòng của khách hàng thông qua đường bưu điện — gửi báo cáo bưu điện</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Xóa bỏ toàn bộ các file ảnh chụp lỗi màn hình cũ đã lưu trong thư mục dự án — dọn dẹp ảnh lỗi</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -833,13 +833,13 @@
         <v>Sử dụng lớp Actions để thực hiện chuỗi hành động di chuyển chuột: `Actions action = new Actions(driver); action.moveToElement(element).perform();` — lớp Actions rê chuột</v>
       </c>
       <c r="F15" t="str">
+        <v>Sử dụng câu lệnh `driver.switchTo().frame(element)` để di chuyển trình duyệt — chuyển frame di chuyển</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Yêu cầu lập trình viên Frontend loại bỏ hoàn toàn tính năng rê chuột ra khỏi website — yêu cầu sửa giao diện</v>
+      </c>
+      <c r="H15" t="str">
         <v>Gọi trực tiếp hàm `element.click()` hai lần liên tiếp vào menu cha — click đúp menu cha</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Sử dụng câu lệnh `driver.switchTo().frame(element)` để di chuyển trình duyệt — chuyển frame di chuyển</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Yêu cầu lập trình viên Frontend loại bỏ hoàn toàn tính năng rê chuột ra khỏi website — yêu cầu sửa giao diện</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -865,10 +865,10 @@
         <v>Đo lường thời gian phản hồi trung bình của API khi tải nặng — đo lường hiệu năng phản hồi</v>
       </c>
       <c r="G16" t="str">
+        <v>Xóa bỏ các tài khoản người dùng cũ trong database khi API được gọi thành công — dọn dẹp tài khoản</v>
+      </c>
+      <c r="H16" t="str">
         <v>Mã hóa toàn bộ dữ liệu gửi đi của API bằng thuật toán bảo mật MD5 — mã hóa dữ liệu gửi</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Xóa bỏ các tài khoản người dùng cũ trong database khi API được gọi thành công — dọn dẹp tài khoản</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -888,19 +888,19 @@
         <v>Mã JavaScript viết trong tab Tests của Postman chạy sau khi nhận được Response. Ví dụ: `pm.test("Status code is 200", function () { pm.response.to.have.status(200); });` giúp tự động hóa khâu xác thực API.</v>
       </c>
       <c r="E17" t="str">
+        <v>Viết tài liệu hướng dẫn sử dụng API bằng ngôn ngữ tiếng Việt có dấu — tài liệu hướng dẫn sử dụng</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Chạy các kịch bản kiểm thử hiệu năng tải trang web bằng cách giả lập click chuột tự động — giả lập click chuột</v>
+      </c>
+      <c r="G17" t="str">
         <v>Viết mã JavaScript để chạy các assertion kiểm tra Response sau khi API gửi request xong (ví dụ kiểm tra Status Code 200) — JavaScript assertions kiểm tra phản hồi</v>
       </c>
-      <c r="F17" t="str">
+      <c r="H17" t="str">
         <v>Viết mã SQL để truy vấn trực tiếp dữ liệu từ máy chủ cơ sở dữ liệu của khách hàng — SQL truy xuất database</v>
       </c>
-      <c r="G17" t="str">
-        <v>Viết tài liệu hướng dẫn sử dụng API bằng ngôn ngữ tiếng Việt có dấu — tài liệu hướng dẫn sử dụng</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Chạy các kịch bản kiểm thử hiệu năng tải trang web bằng cách giả lập click chuột tự động — giả lập click chuột</v>
-      </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>Selenium driver chỉ nhìn thấy tài liệu HTML ở cấp cao nhất (Default Content). Khi phần tử nằm trong thẻ `&lt;iframe&gt;`, ta phải gọi lệnh switch chuyển driver vào trong frame đó. Sau khi thao tác xong, cần gọi `driver.switchTo().defaultContent()` để chuyển driver quay lại trang chính.</v>
       </c>
       <c r="E18" t="str">
+        <v>Vì trình duyệt web đang bị tràn bộ nhớ RAM; cần tắt bớt các tab trình duyệt khác đang mở — tắt bớt tab trình duyệt</v>
+      </c>
+      <c r="F18" t="str">
         <v>Vì phần tử nằm trong một context tài liệu khác; cần gọi câu lệnh `driver.switchTo().frame(iframeElement)` để chuyển ngữ cảnh driver vào trong Iframe trước khi tìm kiếm — chuyển ngữ cảnh driver vào Iframe</v>
       </c>
-      <c r="F18" t="str">
-        <v>Vì trình duyệt web đang bị tràn bộ nhớ RAM; cần tắt bớt các tab trình duyệt khác đang mở — tắt bớt tab trình duyệt</v>
-      </c>
       <c r="G18" t="str">
+        <v>Vì driver của Selenium không hỗ trợ kiểm thử các trang web chứa thẻ Iframe — giới hạn tính năng Selenium</v>
+      </c>
+      <c r="H18" t="str">
         <v>Vì phần tử đó bắt buộc phải hiển thị dạng màu đỏ thì driver mới nhận dạng được — thay đổi màu sắc phần tử</v>
       </c>
-      <c r="H18" t="str">
-        <v>Vì driver của Selenium không hỗ trợ kiểm thử các trang web chứa thẻ Iframe — giới hạn tính năng Selenium</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Nếu chạy song song mà dùng chung một WebDriver instance tĩnh (static driver), các luồng chạy test sẽ tranh chấp điều khiển cùng 1 cửa sổ trình duyệt (luồng này click, luồng kia close tab), dẫn đến sập toàn bộ bộ test. ThreadLocal bọc driver instance giúp cô lập hoàn toàn driver trên từng thread chạy độc lập.</v>
       </c>
       <c r="E19" t="str">
+        <v>Để hệ thống tự động sửa đổi mã nguồn code test khi phát sinh lỗi xung đột tài nguyên giữa các luồng — tự sửa lỗi</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Để ép buộc các máy tính chạy test song song phải có cấu hình bộ vi xử lý tối thiểu là 8 nhân 16 luồng — yêu cầu cấu hình CPU</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Để tự động nén kích thước của các file ảnh chụp màn hình lỗi khi lưu xuống ổ cứng của máy chủ CI/CD — nén ảnh lỗi</v>
+      </c>
+      <c r="H19" t="str">
         <v>Để đảm bảo mỗi luồng chạy test (thread) sở hữu một WebDriver instance riêng biệt độc lập, tránh xung đột chia sẻ tài nguyên driver làm crash trình duyệt và gây lẫn lộn trạng thái test giữa các test case — ThreadLocal cô lập WebDriver instance</v>
       </c>
-      <c r="F19" t="str">
-        <v>Để tự động nén kích thước của các file ảnh chụp màn hình lỗi khi lưu xuống ổ cứng của máy chủ CI/CD — nén ảnh lỗi</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Để ép buộc các máy tính chạy test song song phải có cấu hình bộ vi xử lý tối thiểu là 8 nhân 16 luồng — yêu cầu cấu hình CPU</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Để hệ thống tự động sửa đổi mã nguồn code test khi phát sinh lỗi xung đột tài nguyên giữa các luồng — tự sửa lỗi</v>
-      </c>
       <c r="I19">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -975,19 +975,19 @@
         <v>Playwright/Cypress chạy trên kiến trúc hiện đại (NodeJS process giao tiếp trực tiếp với browser qua CDP/WebSocket thay vì JSON Wire Protocol qua HTTP server như Selenium). Nó tự động chạy các Actionability Checks (Attached, Visible, Stable, Enabled, Receives Events) trước khi click, giúp triệt tiêu hầu hết lỗi Flaky do bất đồng bộ render.</v>
       </c>
       <c r="E20" t="str">
+        <v>Chỉ hỗ trợ chạy các kịch bản test tự động viết bằng ngôn ngữ C++ giúp chạy nhanh gấp 10 lần — hỗ trợ ngôn ngữ C++</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Tự động bỏ qua các lỗi assertion thất bại để đảm bảo toàn bộ test suite luôn báo cáo kết quả Passed — bỏ qua lỗi test</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Tự động tải lại trang web liên tục cho đến khi hệ thống phản hồi thành công mã status code 200 — tự động reload trang</v>
+      </c>
+      <c r="H20" t="str">
         <v>Tự động kiểm tra trước khi tương tác xem phần tử có hiển thị, có kích thước ổn định, có nhận sự kiện click được không (actionability checks) trước khi thực hiện lệnh, loại bỏ việc viết lệnh chờ đợi thủ công — tự động check điều kiện tương tác Actionability</v>
       </c>
-      <c r="F20" t="str">
-        <v>Tự động tải lại trang web liên tục cho đến khi hệ thống phản hồi thành công mã status code 200 — tự động reload trang</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Chỉ hỗ trợ chạy các kịch bản test tự động viết bằng ngôn ngữ C++ giúp chạy nhanh gấp 10 lần — hỗ trợ ngôn ngữ C++</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Tự động bỏ qua các lỗi assertion thất bại để đảm bảo toàn bộ test suite luôn báo cáo kết quả Passed — bỏ qua lỗi test</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Kỹ thuật tốt nhất (Best Practice) là phối hợp với Dev thêm thuộc tính `data-testid` hoặc `data-qa` vào mã nguồn HTML. Thuộc tính này được giữ nguyên khi build và không thay đổi theo CSS style hay logic JS, giúp định vị phần tử bền bỉ 100% qua các đợt refactor.</v>
       </c>
       <c r="E21" t="str">
-        <v>Sử dụng XPath/CSS theo mối quan hệ gia đình (Sibling, Parent-Child) đi từ một gốc phần tử tĩnh ổn định gần nhất, hoặc yêu cầu dev thêm thuộc tính tùy chỉnh chuyên biệt phục vụ test (như `data-testid="submit-btn"`) — sử dụng data-testid và mối quan hệ quan hệ trục</v>
+        <v>Sử dụng đường dẫn tuyệt đối (Absolute XPath) đi từ thẻ gốc html của trang web — đường dẫn tuyệt đối rủi ro cao</v>
       </c>
       <c r="F21" t="str">
-        <v>Sử dụng đường dẫn tuyệt đối (Absolute XPath) đi từ thẻ gốc html của trang web — đường dẫn tuyệt đối rủi ro cao</v>
+        <v>Copy trực tiếp chuỗi class động (như `class="sc-gqjmNp iKqDqf"`) vào locator của script test — sử dụng class động xáo trộn</v>
       </c>
       <c r="G21" t="str">
         <v>Sử dụng chỉ mục cứng (Index) để tìm kiếm phần tử (ví dụ nút bấm thứ 5 trên trang) — sử dụng index cứng dễ gãy</v>
       </c>
       <c r="H21" t="str">
-        <v>Copy trực tiếp chuỗi class động (như `class="sc-gqjmNp iKqDqf"`) vào locator của script test — sử dụng class động xáo trộn</v>
+        <v>Sử dụng XPath/CSS theo mối quan hệ gia đình (Sibling, Parent-Child) đi từ một gốc phần tử tĩnh ổn định gần nhất, hoặc yêu cầu dev thêm thuộc tính tùy chỉnh chuyên biệt phục vụ test (như `data-testid="submit-btn"`) — sử dụng data-testid và mối quan hệ quan hệ trục</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Quản lý dữ liệu test (Test Data Management) là phần khó nhất trong Automation. Teardown script (thường là gọi API DELETE hoặc gọi trực tiếp SQL script xóa dữ liệu test theo tag/prefix nhận diện) giúp trả môi trường về trạng thái sạch (Clean State) sẵn sàng cho lượt chạy tiếp theo.</v>
       </c>
       <c r="E22" t="str">
+        <v>Yêu cầu nhân viên QA hàng ngày phải mở màn hình admin của hệ thống lên và tự bấm xóa bằng tay từng đơn hàng rác — xóa tay thủ công</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Tắt toàn bộ tính năng ghi nhật ký và lưu trữ dữ liệu của máy chủ database của môi trường test — tắt lưu trữ database</v>
+      </c>
+      <c r="G22" t="str">
         <v>Thiết kế các API dọn dẹp (Cleanup APIs/Teardown scripts) chạy ở bước cuối cùng `@AfterSuite` để xóa các dữ liệu rác đã tạo dựa trên ID giao dịch, hoặc kết nối trực tiếp database chạy lệnh SQL DELETE trong mã test — thiết kế Teardown dọn dẹp dữ liệu rác</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Yêu cầu nhân viên QA hàng ngày phải mở màn hình admin của hệ thống lên và tự bấm xóa bằng tay từng đơn hàng rác — xóa tay thủ công</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Tắt toàn bộ tính năng ghi nhật ký và lưu trữ dữ liệu của máy chủ database của môi trường test — tắt lưu trữ database</v>
       </c>
       <c r="H22" t="str">
         <v>Chỉ chạy các kịch bản test API dạng GET để đọc dữ liệu chứ không chạy các API dạng POST/PUT để tránh tạo dữ liệu rác — hạn chế loại test</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1123,13 +1123,13 @@
         <v>Keyword-Driven định nghĩa các từ khóa đại diện cho thao tác (như click_element, enter_text) trong file Excel; BDD sử dụng ngôn ngữ tự nhiên Gherkin (Given-When-Then) để mô tả kịch bản nghiệp vụ liên kết với Step Definitions code — từ khóa thao tác Excel vs ngôn ngữ tự nhiên Gherkin</v>
       </c>
       <c r="F25" t="str">
+        <v>Keyword-Driven bắt buộc phải trả phí bản quyền thương mại; còn BDD hoàn toàn miễn phí — so sánh chi phí bản quyền</v>
+      </c>
+      <c r="G25" t="str">
         <v>Keyword-Driven chỉ dùng cho kiểm thử thiết bị phần cứng; còn BDD chỉ dùng cho kiểm thử ứng dụng di động — phân loại đối tượng test</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>Keyword-Driven chạy nhanh hơn BDD gấp 100 lần do không phải phân tích cú pháp chuỗi văn bản — so sánh hiệu năng tốc độ</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Keyword-Driven bắt buộc phải trả phí bản quyền thương mại; còn BDD hoàn toàn miễn phí — so sánh chi phí bản quyền</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -1149,19 +1149,19 @@
         <v>Khi test suite chạy tự động 1000 test cases trên CI/CD không có người giám sát, nếu có 10 cases bị fail, QA không thể ngồi đoán lỗi. Sử dụng TestNG `ITestListener` giúp lắng nghe sự kiện fail, lập tức kích hoạt `TakesScreenshot` chụp lại trạng thái UI và đính kèm vào báo cáo (như Allure Report) giúp tiết kiệm hàng giờ debug.</v>
       </c>
       <c r="E26" t="str">
-        <v>Để cung cấp bằng chứng trực quan tức thời tại thời điểm lỗi phục vụ debug nhanh; thiết kế bằng cách viết một Class Listener kế thừa `TestListenerAdapter` và ghi đè phương thức `onTestFailure` để gọi hàm chụp ảnh màn hình — thiết kế Test Listener chụp ảnh khi fail</v>
+        <v>Để khóa quyền truy cập vào mã nguồn của lập trình viên đã làm xảy ra lỗi đó — khóa quyền truy cập của dev</v>
       </c>
       <c r="F26" t="str">
         <v>Để hệ thống tự động gửi ảnh chụp lỗi lên mạng xã hội Facebook của công ty nhằm công khai lỗi — công khai lỗi</v>
       </c>
       <c r="G26" t="str">
-        <v>Để khóa quyền truy cập vào mã nguồn của lập trình viên đã làm xảy ra lỗi đó — khóa quyền truy cập của dev</v>
+        <v>Để driver tự động dừng toàn bộ tiến trình chạy test của các test case tiếp theo trong suite — dừng toàn bộ test suite</v>
       </c>
       <c r="H26" t="str">
-        <v>Để driver tự động dừng toàn bộ tiến trình chạy test của các test case tiếp theo trong suite — dừng toàn bộ test suite</v>
+        <v>Để cung cấp bằng chứng trực quan tức thời tại thời điểm lỗi phục vụ debug nhanh; thiết kế bằng cách viết một Class Listener kế thừa `TestListenerAdapter` và ghi đè phương thức `onTestFailure` để gọi hàm chụp ảnh màn hình — thiết kế Test Listener chụp ảnh khi fail</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
